--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_13-11-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_13-11-2025.xlsx
@@ -636,26 +636,26 @@
       <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -736,26 +736,26 @@
       <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -836,26 +836,26 @@
       <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -936,26 +936,26 @@
       <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1036,26 +1036,26 @@
       <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1136,26 +1136,26 @@
       <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1236,26 +1236,26 @@
       <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1336,26 +1336,26 @@
       <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1436,26 +1436,26 @@
       <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1536,26 +1536,26 @@
       <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1636,26 +1636,26 @@
       <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1813,26 +1813,26 @@
       <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1913,26 +1913,26 @@
       <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2013,26 +2013,26 @@
       <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=142.0.7444.135); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6f5d3a235
-	0x7ff6f5a92650
-	0x7ff6f58216dd
-	0x7ff6f587a27e
-	0x7ff6f587a58c
-	0x7ff6f58ced77
-	0x7ff6f58cbaba
-	0x7ff6f586b0ed
-	0x7ff6f586bf63
-	0x7ff6f5d65d60
-	0x7ff6f5d5fe8a
-	0x7ff6f5d81005
-	0x7ff6f5aad73e
-	0x7ff6f5ab4e3f
-	0x7ff6f5a9b7e4
-	0x7ff6f5a9b99f
-	0x7ff6f5a81908
+	0x7ff68989a235
+	0x7ff6895f2650
+	0x7ff6893816dd
+	0x7ff6893da27e
+	0x7ff6893da58c
+	0x7ff68942ed77
+	0x7ff68942baba
+	0x7ff6893cb0ed
+	0x7ff6893cbf63
+	0x7ff6898c5d60
+	0x7ff6898bfe8a
+	0x7ff6898e1005
+	0x7ff68960d73e
+	0x7ff689614e3f
+	0x7ff6895fb7e4
+	0x7ff6895fb99f
+	0x7ff6895e1908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
